--- a/data/pepaws-porch-responses.xlsx
+++ b/data/pepaws-porch-responses.xlsx
@@ -58,10 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -538,6 +541,57 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>felixdswan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-09-08 05:36:53</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Certified with notes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>lifted</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Day 11: you took his weight. Never lift — offer, and let him find his balance. | Watch item in your writing: Lifted, caught, pulled or held him up. | 1 written answer was very short. An assessor may ask you to expand.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -549,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -628,6 +682,262 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Patience with technology; teaching rather than taking over</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>What do you do and say next?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Let's solve this together, how about we turn it off and on again!</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I2" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>does_it_with_him</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>asks_first, plain_language, leaves_a_record, saves_face</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Noticing low mood; presence without fixing; knowing when to escalate</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>What do you say next?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Hey Bruce, i've noticed you seem a bit down today. Do you want to talk about it or I can give you some space if you would prefer.</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>129</v>
+      </c>
+      <c r="I3" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>names_it</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sits_with, offers_presence, marion, escalation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Holding a boundary without rupturing the relationship; knowing what is reportable</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>You have another six days in this house with him. What do you actually say?</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>I know we have our differences in opinion, but I think it is just a matter of our upbringings. I know you're a good person.</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>123</v>
+      </c>
+      <c r="I4" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>says_something, own_position, separates, keeps_relationship, reports</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Assisting without taking over; hazards; never lifting</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Why did you do it that way?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>I held him up becuase it was a serious emergency and there was no room for pride.</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>81</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>offers_not_takes, his_pace, no_lift, hazard, reports_hazard</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>lifted</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Felix Swan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Emergency response: call, don't move, observe, hand over</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The call-taker asks you to tell them exactly what's happened. Type what you say.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>He was dizzy often this week, he reported feeling off this morning, I came out find him on the floor with x symptoms.</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>117</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>age_history</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>triple_zero, location, observations, time_started, not_moved</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -639,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -722,6 +1032,815 @@
         <is>
           <t>seconds</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3:40 pm</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Moving in</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>First afternoon. What do you do?</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unpack first and meet him properly over tea.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10:15 am</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The tea round</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>He hasn't said how he takes it.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ask him how he has it.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6:20 pm</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bin night</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The truck comes at six tomorrow morning.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fetch the notice and show him now.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8:30 am</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The second step</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>He goes down those steps four times a day.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Have a go at fixing it yourself on the weekend.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4:15 pm</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A quiet day</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>He hasn't looked up from the table.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Look at the calendar on the wall.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>examine</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4:15 pm</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A quiet day</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>He hasn't looked up from the table.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sit down at the table with him.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7:05 pm</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kath rings</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bruce is four feet away, pretending to read.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tell her what you've noticed, having first said to him that you would.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5:30 pm</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Something he said</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>What comes out of your mouth first?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>"I'm not comfortable with that, Bruce."</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2:00 pm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The cricket</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The tutorial starts in three minutes.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ask if he'd mind it down for the hour, and tell him when you're done.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8:40 pm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Your boxes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>It's twenty to nine.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Clear them out tonight.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8:05 am</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The second step, again</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>He's already got a hand on the rail.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Take his arm and steady him down.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>took_arm</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8:05 am</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>The second step, again</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>He's off balance, still on his feet, basket going one way.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Get under his arms and hold him up.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>lifted</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5:50 pm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Marion's tomatoes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>He's holding the hose and not really watering anything.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Offer to take over the watering from now on.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7:30 pm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A bit swimmy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>He's already changing the subject.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ask how long, how often, and whether it's happened before — then write it down for the coordinator.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7:50 pm</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>On the kitchen floor</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>What do you do first?</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ring 000 now, and tell him that's what you're doing.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>called</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7:50 pm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>On the kitchen floor</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The call-taker is on the line and staying on it.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Stay on the line, unlock the front door, put a blanket over him.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>stayed_on</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PP-mts80rph-phvraa</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7:50 pm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>On the kitchen floor</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>They ask you to keep talking.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Give the time it started, the cross street, and that he was dizzy three times this week.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>handover</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +3018,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Bands</t>
         </is>
